--- a/data/Bronze/informe_resultados_exito_2026.xlsx
+++ b/data/Bronze/informe_resultados_exito_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\GitHub\Sistema-de-Pronostico-Financiero-Grupo-Exito\data\Bronze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87EA7AD7-2E3A-487E-AFE4-785294A42540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CADE1D5-FF1B-4437-A914-63B2D63756A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7876C4B3-C73F-4249-BC47-92A888B31E57}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10800" xr2:uid="{7876C4B3-C73F-4249-BC47-92A888B31E57}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>año</t>
   </si>
@@ -58,6 +58,15 @@
   </si>
   <si>
     <t>resultado_neto</t>
+  </si>
+  <si>
+    <t>periodo</t>
+  </si>
+  <si>
+    <t>2026-T1</t>
+  </si>
+  <si>
+    <t>2026-T2</t>
   </si>
 </sst>
 </file>
@@ -116,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -130,6 +139,10 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -444,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABC49C9-D7A9-4ECA-B55D-27D6812B512B}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -456,7 +469,7 @@
     <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -478,8 +491,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2026</v>
       </c>
@@ -501,8 +517,11 @@
       <c r="G2" s="4">
         <v>159622</v>
       </c>
+      <c r="H2" s="6" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2026</v>
       </c>
@@ -523,6 +542,9 @@
       </c>
       <c r="G3" s="4">
         <v>156186</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/Bronze/informe_resultados_exito_2026.xlsx
+++ b/data/Bronze/informe_resultados_exito_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\GitHub\Sistema-de-Pronostico-Financiero-Grupo-Exito\data\Bronze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CADE1D5-FF1B-4437-A914-63B2D63756A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C0F5DD-2BF4-4A69-9EF4-5CE60E1ED77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10800" xr2:uid="{7876C4B3-C73F-4249-BC47-92A888B31E57}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>año</t>
   </si>
@@ -58,15 +58,6 @@
   </si>
   <si>
     <t>resultado_neto</t>
-  </si>
-  <si>
-    <t>periodo</t>
-  </si>
-  <si>
-    <t>2026-T1</t>
-  </si>
-  <si>
-    <t>2026-T2</t>
   </si>
 </sst>
 </file>
@@ -139,10 +130,10 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABC49C9-D7A9-4ECA-B55D-27D6812B512B}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -491,9 +482,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="H1" s="5"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
@@ -517,9 +506,7 @@
       <c r="G2" s="4">
         <v>159622</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>8</v>
-      </c>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -543,9 +530,10 @@
       <c r="G3" s="4">
         <v>156186</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H4" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
